--- a/ru/downloads/data-excel/16.6.2.1.xlsx
+++ b/ru/downloads/data-excel/16.6.2.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9294156E-7420-4E7E-BA34-35F9B1EADB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист" sheetId="1" r:id="rId1"/>
@@ -31,12 +32,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -73,9 +68,6 @@
   </si>
   <si>
     <t xml:space="preserve">Источник: Нацстатком,опрос населения по определению уровня доверия населения к  государственным органам исполнительной власти. </t>
-  </si>
-  <si>
-    <t>16.6.2.1a Индекс оценки деятельности к государственным органам исполнительной власти</t>
   </si>
   <si>
     <t>Source: National Statistical Committee, a survey of the population to determine the level of public confidence in the state Executive authorities.</t>
@@ -147,12 +139,6 @@
     <t>Osh city</t>
   </si>
   <si>
-    <t>16.6.2.1а "Мамлекеттик органдардын жана жергиликтүү өз алдынча башкаруу органдарынын ишин баалоо" индекси</t>
-  </si>
-  <si>
-    <t>16.6.2.1a Index "Assessment of the activities of state bodies and local authorities"</t>
-  </si>
-  <si>
     <t>(упай)</t>
   </si>
   <si>
@@ -170,17 +156,26 @@
   <si>
     <t>Маалымат булагы: Улутстатком, калктын мамлекеттик аткаруу бийлик органдарына болгон ишениминин деңгээлин аныктоо үчүн калкты сурамжылоо.</t>
   </si>
+  <si>
+    <t>16.6.2.1 Index "Assessment of the activities of state bodies and local authorities"</t>
+  </si>
+  <si>
+    <t>16.6.2.1 Индекс оценки деятельности к государственным органам исполнительной власти</t>
+  </si>
+  <si>
+    <t>16.6.2.1 "Мамлекеттик органдардын жана жергиликтүү өз алдынча башкаруу органдарынын ишин баалоо" индекси</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;??_р_._-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0_р_._-;\-* #,##0_р_._-;_-* &quot;-&quot;??_р_._-;_-@_-"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial Cyr"/>
@@ -265,6 +260,12 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -323,88 +324,75 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="9">
-    <cellStyle name="Normal 17" xfId="3"/>
-    <cellStyle name="Normal 2" xfId="5"/>
+    <cellStyle name="Normal 17" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 11" xfId="8"/>
-    <cellStyle name="Обычный 2" xfId="6"/>
-    <cellStyle name="Обычный 6" xfId="7"/>
-    <cellStyle name="Обычный 7" xfId="4"/>
-    <cellStyle name="Обычный_Лист5" xfId="2"/>
+    <cellStyle name="Обычный 11" xfId="8" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Обычный 6" xfId="7" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Обычный 7" xfId="4" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Обычный_Лист5" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
     <cellStyle name="Финансовый" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -421,7 +409,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Data"/>
@@ -8147,106 +8135,103 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.85546875" style="8" customWidth="1"/>
-    <col min="2" max="3" width="36.85546875" style="18" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" style="8" customWidth="1"/>
-    <col min="5" max="7" width="9.7109375" style="9" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" style="8" customWidth="1"/>
+    <col min="2" max="3" width="36.85546875" style="17" customWidth="1"/>
+    <col min="4" max="8" width="9.7109375" style="8" customWidth="1"/>
     <col min="9" max="16384" width="8.7109375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="C2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
     </row>
-    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="9"/>
-      <c r="H2" s="9"/>
-    </row>
-    <row r="3" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="M3" s="21"/>
     </row>
-    <row r="4" spans="1:12" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <v>2015</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="10">
         <v>2016</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="10">
         <v>2017</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="10">
         <v>2018</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <v>2019</v>
       </c>
-      <c r="I4" s="20">
+      <c r="I4" s="18">
         <v>2020</v>
       </c>
-      <c r="J4" s="23">
+      <c r="J4" s="18">
         <v>2021</v>
       </c>
-      <c r="K4" s="23">
+      <c r="K4" s="18">
         <v>2022</v>
       </c>
-      <c r="L4" s="23">
+      <c r="L4" s="18">
         <v>2023</v>
       </c>
+      <c r="M4" s="18">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D5" s="6">
         <v>23.47018660578075</v>
@@ -8266,377 +8251,403 @@
       <c r="I5" s="6">
         <v>25.2</v>
       </c>
-      <c r="J5" s="24">
+      <c r="J5" s="6">
         <v>34.075233127500141</v>
       </c>
-      <c r="K5" s="24">
+      <c r="K5" s="6">
         <v>35.305353068702679</v>
       </c>
-      <c r="L5" s="24">
+      <c r="L5" s="6">
         <v>33.991563806511245</v>
       </c>
+      <c r="M5" s="6">
+        <v>38.4</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" s="15" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
+    <row r="6" spans="1:13" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="13" t="s">
+      <c r="D6" s="13">
+        <v>29.364644785598401</v>
+      </c>
+      <c r="E6" s="13">
+        <v>47.911854897613189</v>
+      </c>
+      <c r="F6" s="13">
+        <v>46.22168094057696</v>
+      </c>
+      <c r="G6" s="13">
+        <v>42.644557326068714</v>
+      </c>
+      <c r="H6" s="13">
+        <v>38.677928130166499</v>
+      </c>
+      <c r="I6" s="19">
+        <v>39.4</v>
+      </c>
+      <c r="J6" s="19">
+        <v>44.487602536118636</v>
+      </c>
+      <c r="K6" s="19">
+        <v>49.31549563692068</v>
+      </c>
+      <c r="L6" s="19">
+        <v>43.352267904134116</v>
+      </c>
+      <c r="M6" s="19">
+        <v>52.69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="14">
-        <v>29.364644785598401</v>
-      </c>
-      <c r="E6" s="14">
-        <v>47.911854897613189</v>
-      </c>
-      <c r="F6" s="14">
-        <v>46.22168094057696</v>
-      </c>
-      <c r="G6" s="14">
-        <v>42.644557326068714</v>
-      </c>
-      <c r="H6" s="14">
-        <v>38.677928130166499</v>
-      </c>
-      <c r="I6" s="21">
-        <v>39.4</v>
-      </c>
-      <c r="J6" s="25">
-        <v>44.487602536118636</v>
-      </c>
-      <c r="K6" s="25">
-        <v>49.31549563692068</v>
-      </c>
-      <c r="L6" s="25">
-        <v>43.352267904134116</v>
+      <c r="B7" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="13">
+        <v>43.589550213097176</v>
+      </c>
+      <c r="E7" s="13">
+        <v>37.249330443220579</v>
+      </c>
+      <c r="F7" s="13">
+        <v>35.4</v>
+      </c>
+      <c r="G7" s="13">
+        <v>32.708436184408107</v>
+      </c>
+      <c r="H7" s="13">
+        <v>34.657678561285195</v>
+      </c>
+      <c r="I7" s="19">
+        <v>35.1</v>
+      </c>
+      <c r="J7" s="19">
+        <v>40.668697007891453</v>
+      </c>
+      <c r="K7" s="19">
+        <v>45.444207273635158</v>
+      </c>
+      <c r="L7" s="19">
+        <v>46.016552065013244</v>
+      </c>
+      <c r="M7" s="19">
+        <v>40.54</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="15" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="13" t="s">
+    <row r="8" spans="1:13" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="14">
-        <v>43.589550213097176</v>
-      </c>
-      <c r="E7" s="14">
-        <v>37.249330443220579</v>
-      </c>
-      <c r="F7" s="14">
-        <v>35.4</v>
-      </c>
-      <c r="G7" s="14">
-        <v>32.708436184408107</v>
-      </c>
-      <c r="H7" s="14">
-        <v>34.657678561285195</v>
-      </c>
-      <c r="I7" s="21">
-        <v>35.1</v>
-      </c>
-      <c r="J7" s="25">
-        <v>40.668697007891453</v>
-      </c>
-      <c r="K7" s="25">
-        <v>45.444207273635158</v>
-      </c>
-      <c r="L7" s="25">
-        <v>46.016552065013244</v>
+      <c r="B8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="13">
+        <v>-1.5045585012928908</v>
+      </c>
+      <c r="E8" s="13">
+        <v>16.638282923176</v>
+      </c>
+      <c r="F8" s="13">
+        <v>29.5</v>
+      </c>
+      <c r="G8" s="13">
+        <v>19.463418197866147</v>
+      </c>
+      <c r="H8" s="13">
+        <v>31.583100908489456</v>
+      </c>
+      <c r="I8" s="19">
+        <v>42.7</v>
+      </c>
+      <c r="J8" s="19">
+        <v>50.797011639929529</v>
+      </c>
+      <c r="K8" s="19">
+        <v>46.810603774236895</v>
+      </c>
+      <c r="L8" s="19">
+        <v>57.950845675564537</v>
+      </c>
+      <c r="M8" s="19">
+        <v>59.15</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="15" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="13" t="s">
+    <row r="9" spans="1:13" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="14">
-        <v>-1.5045585012928908</v>
-      </c>
-      <c r="E8" s="14">
-        <v>16.638282923176</v>
-      </c>
-      <c r="F8" s="14">
-        <v>29.5</v>
-      </c>
-      <c r="G8" s="14">
-        <v>19.463418197866147</v>
-      </c>
-      <c r="H8" s="14">
-        <v>31.583100908489456</v>
-      </c>
-      <c r="I8" s="21">
-        <v>42.7</v>
-      </c>
-      <c r="J8" s="25">
-        <v>50.797011639929529</v>
-      </c>
-      <c r="K8" s="25">
-        <v>46.810603774236895</v>
-      </c>
-      <c r="L8" s="25">
-        <v>57.950845675564537</v>
+      <c r="B9" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="13">
+        <v>20.617825255341405</v>
+      </c>
+      <c r="E9" s="13">
+        <v>19.923049320534247</v>
+      </c>
+      <c r="F9" s="13">
+        <v>28.473392889895976</v>
+      </c>
+      <c r="G9" s="13">
+        <v>30.739784066948875</v>
+      </c>
+      <c r="H9" s="13">
+        <v>47.289368826350582</v>
+      </c>
+      <c r="I9" s="19">
+        <v>37.5</v>
+      </c>
+      <c r="J9" s="19">
+        <v>46.848562449074493</v>
+      </c>
+      <c r="K9" s="19">
+        <v>45.450816127137941</v>
+      </c>
+      <c r="L9" s="19">
+        <v>46.481788079470263</v>
+      </c>
+      <c r="M9" s="19">
+        <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="15" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="13" t="s">
+    <row r="10" spans="1:13" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="14">
-        <v>20.617825255341405</v>
-      </c>
-      <c r="E9" s="14">
-        <v>19.923049320534247</v>
-      </c>
-      <c r="F9" s="14">
-        <v>28.473392889895976</v>
-      </c>
-      <c r="G9" s="14">
-        <v>30.739784066948875</v>
-      </c>
-      <c r="H9" s="14">
-        <v>47.289368826350582</v>
-      </c>
-      <c r="I9" s="21">
-        <v>37.5</v>
-      </c>
-      <c r="J9" s="25">
-        <v>46.848562449074493</v>
-      </c>
-      <c r="K9" s="25">
-        <v>45.450816127137941</v>
-      </c>
-      <c r="L9" s="25">
-        <v>46.481788079470263</v>
+      <c r="B10" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="13">
+        <v>34.255749025413991</v>
+      </c>
+      <c r="E10" s="13">
+        <v>30.91794811069628</v>
+      </c>
+      <c r="F10" s="13">
+        <v>32.66592158220363</v>
+      </c>
+      <c r="G10" s="13">
+        <v>27.856595142437566</v>
+      </c>
+      <c r="H10" s="13">
+        <v>37.990783549288928</v>
+      </c>
+      <c r="I10" s="19">
+        <v>40.9</v>
+      </c>
+      <c r="J10" s="19">
+        <v>44.458036086558309</v>
+      </c>
+      <c r="K10" s="19">
+        <v>50.474514452886076</v>
+      </c>
+      <c r="L10" s="19">
+        <v>45.080578284701389</v>
+      </c>
+      <c r="M10" s="19">
+        <v>41.36</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="15" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="13" t="s">
+    <row r="11" spans="1:13" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="14">
-        <v>34.255749025413991</v>
-      </c>
-      <c r="E10" s="14">
-        <v>30.91794811069628</v>
-      </c>
-      <c r="F10" s="14">
-        <v>32.66592158220363</v>
-      </c>
-      <c r="G10" s="14">
-        <v>27.856595142437566</v>
-      </c>
-      <c r="H10" s="14">
-        <v>37.990783549288928</v>
-      </c>
-      <c r="I10" s="21">
-        <v>40.9</v>
-      </c>
-      <c r="J10" s="25">
-        <v>44.458036086558309</v>
-      </c>
-      <c r="K10" s="25">
-        <v>50.474514452886076</v>
-      </c>
-      <c r="L10" s="25">
-        <v>45.080578284701389</v>
+      <c r="B11" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="13">
+        <v>36.443188655233442</v>
+      </c>
+      <c r="E11" s="13">
+        <v>34.131511253975191</v>
+      </c>
+      <c r="F11" s="13">
+        <v>31.207420904442976</v>
+      </c>
+      <c r="G11" s="13">
+        <v>34.060445798837343</v>
+      </c>
+      <c r="H11" s="13">
+        <v>29.962168760513435</v>
+      </c>
+      <c r="I11" s="19">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="J11" s="19">
+        <v>40.532201616746903</v>
+      </c>
+      <c r="K11" s="19">
+        <v>40.14796186663478</v>
+      </c>
+      <c r="L11" s="19">
+        <v>39.506289942950417</v>
+      </c>
+      <c r="M11" s="19">
+        <v>47.13</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="15" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="13" t="s">
+    <row r="12" spans="1:13" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="14">
-        <v>36.443188655233442</v>
-      </c>
-      <c r="E11" s="14">
-        <v>34.131511253975191</v>
-      </c>
-      <c r="F11" s="14">
-        <v>31.207420904442976</v>
-      </c>
-      <c r="G11" s="14">
-        <v>34.060445798837343</v>
-      </c>
-      <c r="H11" s="14">
-        <v>29.962168760513435</v>
-      </c>
-      <c r="I11" s="21">
-        <v>36.700000000000003</v>
-      </c>
-      <c r="J11" s="25">
-        <v>40.532201616746903</v>
-      </c>
-      <c r="K11" s="25">
-        <v>40.14796186663478</v>
-      </c>
-      <c r="L11" s="25">
-        <v>39.506289942950417</v>
+      <c r="B12" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="13">
+        <v>31.422096104099374</v>
+      </c>
+      <c r="E12" s="13">
+        <v>25.580013791572924</v>
+      </c>
+      <c r="F12" s="13">
+        <v>38.456746357297064</v>
+      </c>
+      <c r="G12" s="13">
+        <v>35.486614354431175</v>
+      </c>
+      <c r="H12" s="13">
+        <v>23.647167673376959</v>
+      </c>
+      <c r="I12" s="19">
+        <v>24.7</v>
+      </c>
+      <c r="J12" s="19">
+        <v>33.353175884696697</v>
+      </c>
+      <c r="K12" s="19">
+        <v>29.735683954543184</v>
+      </c>
+      <c r="L12" s="19">
+        <v>26.964612178240138</v>
+      </c>
+      <c r="M12" s="19">
+        <v>35.76</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="15" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="13" t="s">
+    <row r="13" spans="1:13" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="14">
-        <v>31.422096104099374</v>
-      </c>
-      <c r="E12" s="14">
-        <v>25.580013791572924</v>
-      </c>
-      <c r="F12" s="14">
-        <v>38.456746357297064</v>
-      </c>
-      <c r="G12" s="14">
-        <v>35.486614354431175</v>
-      </c>
-      <c r="H12" s="14">
-        <v>23.647167673376959</v>
-      </c>
-      <c r="I12" s="21">
-        <v>24.7</v>
-      </c>
-      <c r="J12" s="25">
-        <v>33.353175884696697</v>
-      </c>
-      <c r="K12" s="25">
-        <v>29.735683954543184</v>
-      </c>
-      <c r="L12" s="25">
-        <v>26.964612178240138</v>
+      <c r="B13" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="13">
+        <v>9.5845758810310464</v>
+      </c>
+      <c r="E13" s="13">
+        <v>12.583671177779776</v>
+      </c>
+      <c r="F13" s="13">
+        <v>16.3</v>
+      </c>
+      <c r="G13" s="13">
+        <v>12.865469106220623</v>
+      </c>
+      <c r="H13" s="13">
+        <v>16.505860491709218</v>
+      </c>
+      <c r="I13" s="19">
+        <v>-8</v>
+      </c>
+      <c r="J13" s="19">
+        <v>10.46405303463253</v>
+      </c>
+      <c r="K13" s="19">
+        <v>12.912087912087852</v>
+      </c>
+      <c r="L13" s="19">
+        <v>15.46142526802614</v>
+      </c>
+      <c r="M13" s="19">
+        <v>24.89</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="15" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="13" t="s">
+    <row r="14" spans="1:13" s="14" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="14">
-        <v>9.5845758810310464</v>
-      </c>
-      <c r="E13" s="14">
-        <v>12.583671177779776</v>
-      </c>
-      <c r="F13" s="14">
-        <v>16.3</v>
-      </c>
-      <c r="G13" s="14">
-        <v>12.865469106220623</v>
-      </c>
-      <c r="H13" s="14">
-        <v>16.505860491709218</v>
-      </c>
-      <c r="I13" s="21">
-        <v>-8</v>
-      </c>
-      <c r="J13" s="25">
-        <v>10.46405303463253</v>
-      </c>
-      <c r="K13" s="25">
-        <v>12.912087912087852</v>
-      </c>
-      <c r="L13" s="25">
-        <v>15.46142526802614</v>
+      <c r="B14" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="13">
+        <v>16.932905463929991</v>
+      </c>
+      <c r="E14" s="13">
+        <v>40.826475513397519</v>
+      </c>
+      <c r="F14" s="13">
+        <v>42.862633597475771</v>
+      </c>
+      <c r="G14" s="13">
+        <v>38.281575289845613</v>
+      </c>
+      <c r="H14" s="13">
+        <v>31.381881643661952</v>
+      </c>
+      <c r="I14" s="20">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="J14" s="20">
+        <v>43.479082661290349</v>
+      </c>
+      <c r="K14" s="20">
+        <v>41.117034465658314</v>
+      </c>
+      <c r="L14" s="20">
+        <v>33.453947368420813</v>
+      </c>
+      <c r="M14" s="20">
+        <v>33.92</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="15" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="14">
-        <v>16.932905463929991</v>
-      </c>
-      <c r="E14" s="14">
-        <v>40.826475513397519</v>
-      </c>
-      <c r="F14" s="14">
-        <v>42.862633597475771</v>
-      </c>
-      <c r="G14" s="14">
-        <v>38.281575289845613</v>
-      </c>
-      <c r="H14" s="14">
-        <v>31.381881643661952</v>
-      </c>
-      <c r="I14" s="22">
-        <v>38.799999999999997</v>
-      </c>
-      <c r="J14" s="26">
-        <v>43.479082661290349</v>
-      </c>
-      <c r="K14" s="26">
-        <v>41.117034465658314</v>
-      </c>
-      <c r="L14" s="26">
-        <v>33.453947368420813</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="16" t="s">
+    <row r="15" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-    </row>
-    <row r="20" spans="2:3" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
+      <c r="C15" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="1.1811023622047245" right="0.59055118110236227" top="0.98425196850393704" bottom="0.98425196850393704" header="0" footer="0"/>
